--- a/www/download/COUNTRY.GBR.zdW16.xlsx
+++ b/www/download/COUNTRY.GBR.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Reino Unido</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.659582747953644</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.694463735103753</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.666107136671862</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.61185655634893</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.545911125668741</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>0.549329817622501</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>0.542702550159283</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>0.499580352503897</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>0.539595519198809</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>0.639190018408673</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.646784510804535</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>0.623596906959342</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.630791454037381</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>0.639194104073584</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.607009748576562</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>27.482</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>27.711</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>27.944</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>28.225</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>28.852</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>29.14</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>29.373</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>29.629</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>29.152</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>29.227</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>29.372</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>29.693</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>30.044</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>30.726</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>24.36</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24.562</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>24.749</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>24.826</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>25.083</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>25.395</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>25.593</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>25.752</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>25.974</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>25.474</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>25.395</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>25.475</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>25.639</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>26.412</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>45942.081</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>46316.584</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>46337.779</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>46526.438</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>46579.213</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>47672.921</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>48018.735</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>48556.582</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>48349.912</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>47596.655</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>47795.13</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>48075.43</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>49129.723</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>49988.879</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>51360.176</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>40619.228</t>
+          <t>39866009120.1593</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40936.533</t>
+          <t>39699539196.3381</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>40901.692</t>
+          <t>39907141112.5945</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>40782.353</t>
+          <t>40678071322.8679</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40825.354</t>
+          <t>41266575902.203</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>41818.452</t>
+          <t>41861886305.1773</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>42012.411</t>
+          <t>42635055147.3843</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>42413.228</t>
+          <t>41710639943.4709</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>42235.907</t>
+          <t>39770335211.8969</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>41343.691</t>
+          <t>39849559590.0174</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>41269.384</t>
+          <t>40319081134.0561</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>41448.212</t>
+          <t>42589119501.2956</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>42174.181</t>
+          <t>43843688824.4419</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>42943.732</t>
+          <t>45267810229.233</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>43877.235</t>
+          <t>43269247320.6309</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>26458533892.2682</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>28505225172.0937</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30241111511.9897</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30949569150.1305</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>33769836690.9974</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>33803906035.8505</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>34435322499.6175</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>32293860116.9613</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>28505815491.135</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>25801989816.1215</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>23044974452.3558</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>22369811696.5994</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>22672266698.3564</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>26516036932.2105</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>22043443479.8885</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1031758.32286009</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1059024.94707846</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1066263.99280101</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>971349.006152142</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>800429.017792451</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>827350.342462022</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>757426.752695387</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>632906.554388063</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>622555.025212878</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>746753.658326124</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>698098.607755269</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>693131.520311903</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>682878.887770125</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>692537.120981167</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>602299.380051553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>183064.042541026</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>178861.662338107</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>179403.333232821</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>193178.459090107</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>211964.137371633</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>234203.764136763</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>248814.665274736</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>279245.915568653</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>301655.25045735</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>278502.40692338</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>308117.042989271</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>328688.48179923</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>328101.017182514</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>329371.44690586</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>338852.331387414</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>361638.114769335</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>354854.755256728</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>359334.269507701</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>398764.758849475</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>445804.528746797</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>488452.243747192</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>525686.377380415</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>576912.363274817</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>599946.331474916</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549380.537125515</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>614121.800792383</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>691656.660011786</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>695522.703691504</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>713950.645840747</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>684812.284380378</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.53520327941791</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.436106284123531</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.35251946621683</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.317703416230855</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.208929565563563</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.237089345700159</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.220038261598006</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.313352688293955</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.48165931310174</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.602345063099274</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.790819255856505</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.852863696939429</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.8601660593141</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.61953809725743</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.990489146581464</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.659582747953644</t>
+          <t>1086.14671150526</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.694463735103753</t>
+          <t>1160.54169742259</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.666107136671862</t>
+          <t>1221.91246159399</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.61185655634893</t>
+          <t>1246.65951623824</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.545911125668741</t>
+          <t>1346.32367304539</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.549329817622501</t>
+          <t>1331.12447473324</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.542702550159283</t>
+          <t>1345.49769466719</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.499580352503897</t>
+          <t>1254.03308935078</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.539595519198809</t>
+          <t>1097.47499388369</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.639190018408673</t>
+          <t>1012.87547366419</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.646784510804535</t>
+          <t>907.461092827557</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.623596906959342</t>
+          <t>878.108408109887</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.630791454037381</t>
+          <t>884.288260008442</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.639194104073584</t>
+          <t>1021.4189881437</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.607009748576562</t>
+          <t>834.599556258083</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>29844693255.7598</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>31095096126.757</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>32715667222.9166</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.016</t>
+          <t>35328033340.6077</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.206</t>
+          <t>38163218414.1861</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>38717994373.2967</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.356</t>
+          <t>39516454223.351</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.563</t>
+          <t>36986576575.7733</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>32659168232.7155</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>29275566009.1267</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>25898342254.3837</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>28275826125.3509</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>27972209255.4336</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>33987076780.4995</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>27764747070.0216</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>26519199407.3235</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>27076419593.1905</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>28053972851.479</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>29477453736.1063</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>31381717710.2355</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>31673092194.0933</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>31418622215.2435</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.789</t>
+          <t>28289464239.9815</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.679</t>
+          <t>25905389404.2135</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>20592381932.4897</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>16134610325.3164</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>16984207763.13</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>16567584346.0624</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.594</t>
+          <t>20984351250.0214</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>14135895638.4584</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3325493848.43634</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.366</t>
+          <t>4018676533.56645</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4661694371.43764</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.289</t>
+          <t>5850579604.50143</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5.104</t>
+          <t>6781500703.95058</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5.515</t>
+          <t>7044902179.20348</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5.884</t>
+          <t>8097832008.10741</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.825</t>
+          <t>8697112335.79177</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>6.773</t>
+          <t>6753778828.50197</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>5.724</t>
+          <t>8683184076.63693</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>5.689</t>
+          <t>9763731929.06731</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>6.119</t>
+          <t>11291618362.2209</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6.237</t>
+          <t>11404624909.3712</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>6.399</t>
+          <t>13002725530.4781</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.939</t>
+          <t>13628851431.5633</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.754</t>
+          <t>1667.45599343186</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>1666.66122465597</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.982</t>
+          <t>1652.6603903188</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>1642.72750342383</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.027</t>
+          <t>1627.6104931627</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.177</t>
+          <t>1646.71990549321</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.576</t>
+          <t>1641.55866838589</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>1646.98772910842</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>5.038</t>
+          <t>1626.08404558405</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.188</t>
+          <t>1622.97601476015</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>4.276</t>
+          <t>1625.09879897618</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>4.597</t>
+          <t>1627.01519136408</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.659</t>
+          <t>1644.92300791763</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4.808</t>
+          <t>1654.22696456086</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>5.283</t>
+          <t>1661.26135847342</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1671.71535250949</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1671.41510363855</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1658.23714112443</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>1648.41234715771</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.057</t>
+          <t>1632.63977425054</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>1652.32639777415</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>1647.86325731107</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.664</t>
+          <t>1653.10257749182</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.538</t>
+          <t>1631.84419228967</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1632.70631827557</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.161</t>
+          <t>1635.30741866133</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.314</t>
+          <t>1636.77755897388</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2.355</t>
+          <t>1654.58938787114</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1663.85565881586</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2.666</t>
+          <t>1671.55425638547</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>379119.035305813</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>371486.988693439</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>389765.507029798</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>449315.522273911</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>528165.969284351</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>571108.020967771</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>635886.877124667</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>722382.36318658</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>742667.461475491</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>586210.978613664</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>638591.807459606</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>741853.494169986</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>739091.594865317</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>726354.981327779</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>751599.243421443</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7347678426.88826</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7301298248.61772</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6993429673.33413</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7214809295.41306</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>7282445317.16994</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>7325231289.05372</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>7545165493.20962</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7282009797.17146</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>7317504781.49453</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6477655658.37173</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>6640964559.99126</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7793217712.08943</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>7726828876.49475</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6924031333.64915</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>6227764764.01889</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>376955.940072648</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>373614.798491456</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>398919.78995268</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>451644.633857295</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>538701.438938222</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>580746.949007115</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>642604.030631942</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>730925.866705637</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>752826.226162057</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>592379.914755642</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>661050.196552821</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>743823.35008859</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>753205.931491608</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>744800.839494408</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>770102.729247112</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45942.081</t>
+          <t>36896557832.477</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>46316.584</t>
+          <t>38699247405.3137</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>46337.779</t>
+          <t>41020251451.0644</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>46526.438</t>
+          <t>42857295447.7483</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>46579.213</t>
+          <t>46741777643.091</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>47672.921</t>
+          <t>47118729236.0895</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>48018.735</t>
+          <t>47741824478.8031</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>48556.582</t>
+          <t>45010431071.356</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>48349.912</t>
+          <t>40746796781.1019</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>47596.655</t>
+          <t>36278517134.8303</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>47795.13</t>
+          <t>34244067070.8497</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>48075.43</t>
+          <t>36210599209.575</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>49129.723</t>
+          <t>36720062067.816</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>49988.879</t>
+          <t>42258776452.0857</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>51360.176</t>
+          <t>35331406848.1758</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>40619.228</t>
+          <t>2163.09523316502</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40936.533</t>
+          <t>-2127.80979801756</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>40901.692</t>
+          <t>-9154.28292288202</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>40782.353</t>
+          <t>-2329.11158338393</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>40825.354</t>
+          <t>-10535.4696538701</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>41818.452</t>
+          <t>-9638.92803934322</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>42012.411</t>
+          <t>-6717.15350727502</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>42413.228</t>
+          <t>-8543.50351905727</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>42235.907</t>
+          <t>-10158.7646865659</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>41343.691</t>
+          <t>-6168.93614197739</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>41269.384</t>
+          <t>-22458.3890932149</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>41448.212</t>
+          <t>-1969.85591860408</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>42174.181</t>
+          <t>-14114.3366262917</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>42943.732</t>
+          <t>-18445.8581666282</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>43877.235</t>
+          <t>-18503.4858256691</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>46451.482</t>
+          <t>-29548879405.5887</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>46184.029</t>
+          <t>-31397949156.696</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>46390.289</t>
+          <t>-34026821777.7302</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>47256.045</t>
+          <t>-35642486152.3352</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>48136.853</t>
+          <t>-39459332325.9211</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>49116.754</t>
+          <t>-39793497947.0358</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>49701.477</t>
+          <t>-40196658985.5934</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>48611.915</t>
+          <t>-37728421274.1846</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>46587.308</t>
+          <t>-33429291999.6073</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>46824.306</t>
+          <t>-29800861476.4585</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>47453.278</t>
+          <t>-27603102510.8585</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>50438.265</t>
+          <t>-28417381497.4856</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>51937.711</t>
+          <t>-28993233191.3212</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>53714.401</t>
+          <t>-35334745118.4366</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>43269.247</t>
+          <t>-29103642084.1569</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>593229.58524</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>571158.69404</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>625067.61612</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>708045.04014</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>823390.4364</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>867937.5936</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>929011.66551</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>1046746.52912</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>992626.84908</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>811597.4672</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>829729.20816</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>886263.2156</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>892057.10762</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>919263.79836</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>995835.73644</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20180.486</t>
+          <t>0.141441109748662</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20010.231</t>
+          <t>0.131532313014645</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>19924.273</t>
+          <t>0.134075662334223</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19706.173</t>
+          <t>0.136222995156123</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19620.784</t>
+          <t>0.134072085385937</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20071.996</t>
+          <t>0.134759906224355</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>20179.764</t>
+          <t>0.132596448057229</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>20189.42</t>
+          <t>0.128277932930581</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>19996.673</t>
+          <t>0.126869830801739</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>20201.295</t>
+          <t>0.119650525408979</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>20228.88</t>
+          <t>0.123058932044719</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>20239.165</t>
+          <t>0.125786445384798</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>20682.515</t>
+          <t>0.125314397952067</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>20883.69</t>
+          <t>0.129142142458311</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>21410.079</t>
+          <t>0.135002698050306</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>814364.84151</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>825251.15572</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>889592.63064</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>1016324.81265</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>1205611.9926</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1255216.7712</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1356310.19199</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1563151.9456</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>1467267.55844</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>1243975.93376</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1266537.75147</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>1332411.9968</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>1347599.10674</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>1366098.33294</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>1470612.29592</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>29806.385</t>
+          <t>914961.77223</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>31923.763</t>
+          <t>929214.82776</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>33912.808</t>
+          <t>1005347.28294</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>34700.381</t>
+          <t>1157488.61829</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>37716.088</t>
+          <t>1372776.5652</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>37944.441</t>
+          <t>1428196.6404</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>38647.625</t>
+          <t>1544886.78882</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>36096.554</t>
+          <t>1789003.50168</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>32063.037</t>
+          <t>1678670.35172</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>29155.931</t>
+          <t>1424806.35456</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>26093.852</t>
+          <t>1460973.45285</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>25464.028</t>
+          <t>1544799.1952</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>25821.591</t>
+          <t>1573778.45506</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>29926.225</t>
+          <t>1593656.75232</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>22043.443</t>
+          <t>1729253.94108</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>3339585.52863</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>3366478.16412</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>3729779.88558</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>4289149.10328</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5104312.5318</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>5514643.3032</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8.71</t>
+          <t>5884164.35313</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>6824812.03056</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>6773486.56532</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>5724219.55072</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>5689083.36321</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>6118673.7096</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>6237408.53624</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>6399489.56652</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>99.05</t>
+          <t>6939428.91342</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1202753.0301151</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1259534.58833344</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>1261619.68020916</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1305026.35262288</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>1335693.86646553</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1365691.18348702</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>1411361.66709022</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>1467706.81978595</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>1446069.74915061</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>1397650.914282</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>1432625.40285</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>1457225.30182284</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1483718.99528741</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>1487557.16764181</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>1525421.33905495</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1071119.97476056</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1119738.46156344</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1119019.74877351</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1148148.83766867</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1173987.50576042</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1202369.81475337</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1242249.86138979</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1286472.3413235</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1265685.82390265</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1218914.94930627</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1241962.44147</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1255510.17924753</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1272621.5668742</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1277579.93231556</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1297693.08978848</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>472354.68327</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>442800.65964</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>500072.70852</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>584280.73752</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>684345.8256</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>743152.8144</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>780219.29301</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>875472.77992</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>859351.09448</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>684905.8768</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>700092.52299</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>769646.2164</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>781637.0955</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>826443.79326</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>936841.62624</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>40619228000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>40936533000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>40901692000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>40782353000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>40825354000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>41818452000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>42012411000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>42413228000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>42235907000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>41343691000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>41269384000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>41448212000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>42174181000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>42943732000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>43877235000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>45942081317.6658</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>46316583936.9278</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>46337778671.5812</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>46526438498.5265</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>46579212759.3678</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>47672921228.5797</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>48018735318.0445</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>48556582008.6673</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>48349911573.3506</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>47596654590.3695</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>47795129925.2147</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>48075430462.1808</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>49129722694.0578</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>49988879413.4637</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>51360176081.6999</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>20180485660.8344</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20010230860.7269</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19924273143.2232</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>19706172530.3448</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>19620783548.2971</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>20071995721.2687</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>20179763889.5056</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>20189419713.338</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>19996672701.7467</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>20201294932.5158</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>20228879741.8376</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>20239164659.8303</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>20682515213.3546</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>20883690266.7193</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>21410079325.958</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>27482000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>27711000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>27944000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>28225000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>28530000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>28852000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>29140000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>29373000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>29629000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>29152000</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>29227000</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>29372000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>29693000</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>30044000</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>30726000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>24360000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>24562000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>24749000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>24826000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>25083000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>25395000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>25593000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>25752000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>25974000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>25474000</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>25395000</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>25475000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>25639000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>25960000</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>26412000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>45942081317.6658</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>46316583936.9278</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>46337778671.5812</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>46526438498.5265</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>46579212759.3678</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>47672921228.5797</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>48018735318.0445</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>48556582008.6673</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>48349911573.3506</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>47596654590.3695</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>47795129925.2147</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>48075430462.1808</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>49129722694.0578</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>49988879413.4637</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>51360176081.6999</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>40619228000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>40936533000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>40901692000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>40782353000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>40825354000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>41818452000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>42012411000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>42413228000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>42235907000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>41343691000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>41269384000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>41448212000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>42174181000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>42943732000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>43877235000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2753696.94801</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2733398.31016</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2982311.53914</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3407164.60152</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>4026986.9886</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4176743.964</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4576033.40775</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>5289599.5344</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>5038019.96732</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4188352.32544</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>4275965.10708</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4597391.3084</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4659264.13744</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4808146.66533</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>5283463.35134482</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1387317.97161</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1372015.4874</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1505418.4902</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1741769.35581</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2057122.3908</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2171349.4548</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2325106.08183</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2664476.2816</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2538021.4462</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2109712.23136</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2161065.97584</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2314445.4116</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2355415.55056</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2420100.54558</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2666095.56732</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4058998.39379152</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4227130.27529867</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4417710.53151226</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4537367.28716014</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4714590.26076747</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4970449.23844959</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5081366.44092972</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5276210.6213368</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>5422518.85829341</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>5580435.47157393</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>5578695.03321</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>5655225.86546538</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>5603508.34321472</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>5740323.3149296</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>5814889.71902551</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
